--- a/Guide/物料清单-机械.xlsx
+++ b/Guide/物料清单-机械.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ROS2轮足\Aidlux\Rhino-Pi-X1-ROS2HomeRobots\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71917C75-11B0-40D9-812D-09DACCF265DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A99A4E-B101-4C89-BF08-490F1FA53529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15760" xr2:uid="{3DBED01D-30EC-4F30-B2D8-D5DB2798D1C0}"/>
   </bookViews>
@@ -362,7 +362,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -445,17 +445,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -496,7 +485,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1376,21 +1365,21 @@
       <c r="I33" s="8"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
       <c r="E34" s="9">
         <v>2</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
